--- a/artfynd/A 4149-2024 artfynd.xlsx
+++ b/artfynd/A 4149-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117807081</v>
+        <v>117807093</v>
       </c>
       <c r="B2" t="n">
         <v>97836</v>
@@ -708,21 +708,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2024-06-15-Hygg1, Ög</t>
+          <t>2024-06-15-Hygg2, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562618</v>
+        <v>562656</v>
       </c>
       <c r="R2" t="n">
-        <v>6454329</v>
+        <v>6454310</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,14 +779,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas Lindebring, Carina Faxén, Karin Wilhelmsson</t>
+          <t>Jonas Lindebring, Karin Wilhelmsson, Carina Faxén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117807093</v>
+        <v>117807081</v>
       </c>
       <c r="B3" t="n">
         <v>97836</v>
@@ -815,25 +819,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2024-06-15-Hygg2, Ög</t>
+          <t>2024-06-15-Hygg1, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562656</v>
+        <v>562618</v>
       </c>
       <c r="R3" t="n">
-        <v>6454310</v>
+        <v>6454329</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jonas Lindebring, Karin Wilhelmsson, Carina Faxén</t>
+          <t>Jonas Lindebring, Carina Faxén, Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 4149-2024 artfynd.xlsx
+++ b/artfynd/A 4149-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117807093</v>
       </c>
       <c r="B2" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>117807081</v>
       </c>
       <c r="B3" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4149-2024 artfynd.xlsx
+++ b/artfynd/A 4149-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>117807081</v>
       </c>
       <c r="B2" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,12 +780,7 @@
         <v>117807093</v>
       </c>
       <c r="B3" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4149-2024 artfynd.xlsx
+++ b/artfynd/A 4149-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117807081</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,8 +890,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117807093</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>